--- a/test_data/WTA/WTA Pillar2 Information/WTA Pillar2 Information_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Information/WTA Pillar2 Information_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Info_01</t>
+          <t>P2Info_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Information loads with the jurisdiction/category placeholder</t>
+          <t>Selecting only a jurisdiction keeps the placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load with the 'Select Jurisdictions and Categories' placeholder shown.</t>
+          <t>Checking a country without also checking a GMT category must NOT render content.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in and on Pillar 2 &gt; Information.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Information
-2. Verify the placeholder text is visible</t>
+2. Check 'Australia' only
+3. Verify the placeholder is still shown</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load with the 'Select Jurisdictions and Categories' placeholder shown.</t>
+          <t>Checking a country without also checking a GMT category must NOT render content.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Information loaded with the jurisdiction/category placeholder visible.</t>
+          <t>Selecting Australia alone left the placeholder in place, confirming a GMT category is also required.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder instruction text is visible</t>
+          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Info_02</t>
+          <t>P2Info_05</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +581,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>All 9 GMT categories are listed in the left panel</t>
+          <t>Switching region tabs changes the visible country list</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The category checklist must show all 9 known Pillar Two GMT topics.</t>
+          <t>Clicking 'Europe' must hide Asia Pacific-only countries like 'Australia'.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -599,205 +600,28 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Information
-2. Verify each of the 9 GMT categories is visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>The category checklist must show all 9 known Pillar Two GMT topics.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>All 9 GMT categories were visible in the left panel.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 9 GMT categories are visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Info_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Information</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Selecting only a jurisdiction keeps the placeholder</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Checking a country without also checking a GMT category must NOT render content.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Pillar 2 &gt; Information.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Information
-2. Check 'Australia' only
-3. Verify the placeholder is still shown</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Checking a country without also checking a GMT category must NOT render content.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia alone left the placeholder in place, confirming a GMT category is also required.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Info_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Information</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting a jurisdiction and a category renders content</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' AND the 'Scope of GMT' category must replace the placeholder with a 'Showing information of Australia' content header.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Pillar 2 &gt; Information.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia / Category: Scope of GMT</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Information
-2. Check 'Australia'
-3. Check 'Scope of GMT'
-4. Verify 'Showing information of' content header appears</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' AND the 'Scope of GMT' category must replace the placeholder with a 'Showing information of Australia' content header.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia and 'Scope of GMT' rendered the 'Showing information of Australia' content header, replacing the placeholder.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Content header 'Showing information of ...' is visible</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2Info_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Information</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Switching region tabs changes the visible country list</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Europe' must hide Asia Pacific-only countries like 'Australia'.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Pillar 2 &gt; Information.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Information
 2. Click the 'Europe' region tab
 3. Verify 'Australia' is no longer listed</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Europe' must hide Asia Pacific-only countries like 'Australia'.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Switching to the 'Europe' region tab hid 'Australia' from the list.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is not listed under 'Europe'</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Information/WTA Pillar2 Information_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Information/WTA Pillar2 Information_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Info_03</t>
+          <t>P2Info_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,44 +530,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Selecting only a jurisdiction keeps the placeholder</t>
+          <t>Pillar 2 &gt; Information loads with the jurisdiction/category placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Checking a country without also checking a GMT category must NOT render content.</t>
+          <t>The page must load with the 'Select Jurisdictions and Categories' placeholder shown.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Pillar 2 &gt; Information.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Information
-2. Check 'Australia' only
-3. Verify the placeholder is still shown</t>
+2. Verify the placeholder text is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Checking a country without also checking a GMT category must NOT render content.</t>
+          <t>The page must load with the 'Select Jurisdictions and Categories' placeholder shown.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia alone left the placeholder in place, confirming a GMT category is also required.</t>
+          <t>Pillar 2 &gt; Information loaded with the jurisdiction/category placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
+          <t>[PASS] Placeholder instruction text is visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -571,7 +578,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Info_05</t>
+          <t>P2Info_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,12 +588,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching region tabs changes the visible country list</t>
+          <t>All 9 GMT categories are listed in the left panel</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must hide Asia Pacific-only countries like 'Australia'.</t>
+          <t>The category checklist must show all 9 known Pillar Two GMT topics.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -602,28 +609,27 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Information
-2. Click the 'Europe' region tab
-3. Verify 'Australia' is no longer listed</t>
+2. Verify each of the 9 GMT categories is visible</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Europe' must hide Asia Pacific-only countries like 'Australia'.</t>
+          <t>The category checklist must show all 9 known Pillar Two GMT topics.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Switching to the 'Europe' region tab hid 'Australia' from the list.</t>
+          <t>Missing GMT categories: ['Scope of GMT', 'Income Inclusion Rule (IIR)', 'Undertaxed Profits Rule (UTPR)', 'Qualified Domestic Minimum Top-up Tax (QDMTT)', 'Safe Harbours under GloBE Rule', 'Filing obligations of GMT', 'Penalties under GMT', 'Payment obligations of GMT', 'Qualified Refundable Tax Credits under GMT'].</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Australia' is not listed under 'Europe'</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] All 9 GMT categories are visible</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
